--- a/output/laminas_comunales/comunal_o_ocup_a_2019_biobio.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2019_biobio.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,181 +375,181 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="C2">
-        <v>41.7563514709473</v>
+        <v>63.2756042480469</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Hualpén</t>
         </is>
       </c>
       <c r="C3">
-        <v>41.2914619445801</v>
+        <v>62.6078567504883</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C4">
-        <v>41.0530052185059</v>
+        <v>62.5621109008789</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="C5">
-        <v>40.7333030700684</v>
+        <v>62.5333099365234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hualpén</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="C6">
-        <v>40.4910736083984</v>
+        <v>62.0482482910156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="C7">
-        <v>40.4820442199707</v>
+        <v>61.9262962341309</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C8">
-        <v>40.0839614868164</v>
+        <v>60.8247375488281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="C9">
-        <v>39.5268745422363</v>
+        <v>60.6280822753906</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Talcahuano</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="C10">
-        <v>39.3622856140137</v>
+        <v>59.3330841064453</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="C11">
-        <v>39.0093879699707</v>
+        <v>59.2654991149902</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="C12">
-        <v>38.4034767150879</v>
+        <v>59.0764312744141</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="C13">
-        <v>37.9488563537598</v>
+        <v>58.9754943847656</v>
       </c>
     </row>
     <row r="14">
@@ -564,37 +564,37 @@
         </is>
       </c>
       <c r="C14">
-        <v>36.8649787902832</v>
+        <v>58.080265045166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="C15">
-        <v>36.5057678222656</v>
+        <v>57.6388893127441</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="C16">
-        <v>35.5565605163574</v>
+        <v>57.3166961669922</v>
       </c>
     </row>
     <row r="17">
@@ -609,67 +609,67 @@
         </is>
       </c>
       <c r="C17">
-        <v>35.4734039306641</v>
+        <v>56.4919204711914</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="C18">
-        <v>35.2649765014648</v>
+        <v>55.8794212341309</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="C19">
-        <v>35.0612831115723</v>
+        <v>55.5584487915039</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="C20">
-        <v>34.3627014160156</v>
+        <v>54.9708671569824</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>Hualpén</t>
         </is>
       </c>
       <c r="C21">
-        <v>33.6014862060547</v>
+        <v>54.9415512084961</v>
       </c>
     </row>
     <row r="22">
@@ -684,187 +684,3157 @@
         </is>
       </c>
       <c r="C22">
-        <v>33.3594779968262</v>
+        <v>54.5218772888184</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="C23">
-        <v>33.1601524353027</v>
+        <v>54.498893737793</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="C24">
-        <v>32.905876159668</v>
+        <v>54.3327560424805</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C25">
-        <v>32.5822257995605</v>
+        <v>54.2863159179688</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="C26">
-        <v>29.9088973999023</v>
+        <v>54.1701927185059</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="C27">
-        <v>29.7146682739258</v>
+        <v>54.0107650756836</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="C28">
-        <v>29.0304393768311</v>
+        <v>53.3988037109375</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="C29">
-        <v>28.7660083770752</v>
+        <v>53.2553405761719</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="C30">
-        <v>28.201114654541</v>
+        <v>52.9826354980469</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="C31">
-        <v>28.1622905731201</v>
+        <v>52.9380950927734</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="C32">
-        <v>27.9324245452881</v>
+        <v>52.1872406005859</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="C33">
-        <v>26.0736198425293</v>
+        <v>52.0623626708984</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>51.8061447143555</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nacimiento</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>51.706470489502</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>51.1599082946777</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>51.1401672363281</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8108</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>San Pedro de la Paz</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>50.9093551635742</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>8104</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>50.8697509765625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>50.7346458435059</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tomé</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>50.6189193725586</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8308</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Quilaco</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>50.363899230957</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>50.2911682128906</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>50.0772323608398</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Hualpén</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>50.0530967712402</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>49.8063011169434</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>49.7996711730957</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cabrero</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>49.6323127746582</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>49.5689811706543</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>8103</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Chiguayante</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>49.5449752807617</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>49.2532196044922</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Antuco</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>49.1434020996094</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>48.294075012207</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>48.0372848510742</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>47.5517082214355</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>8204</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Contulmo</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>47.5153198242188</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Hualqui</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>46.9445915222168</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>8307</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Negrete</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>46.6389465332031</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>46.5706787109375</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Los Alamos</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>46.5081825256348</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>46.4414825439453</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>San Rosendo</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>46.244499206543</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Nacimiento</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>45.5647125244141</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>44.9030303955078</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Cabrero</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>44.5433731079102</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>8312</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tucapel</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>44.372501373291</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Los Alamos</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>44.2024612426758</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Quilleco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>44.1978950500488</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hualqui</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>44.0335998535156</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>8312</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tucapel</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>43.290283203125</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>8202</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>43.2031860351562</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>8202</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>43.0477447509766</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>42.9304428100586</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>San Rosendo</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>42.5925941467285</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Santa Juana</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>42.5406761169434</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Quilleco</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>42.0316925048828</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tomé</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>41.9598922729492</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>8108</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>San Pedro de la Paz</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>41.7563514709473</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>41.2914619445801</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>41.2081184387207</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>41.0530052185059</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>40.7333030700684</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>40.5749778747559</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Hualpén</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>40.4910736083984</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>40.4820442199707</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>8103</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Chiguayante</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>40.0839614868164</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Santa Juana</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>40.0679016113281</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Antuco</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>40.0501174926758</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Antuco</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>39.6327667236328</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>39.5268745422363</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>39.3622856140137</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>8207</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tirúa</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>39.2818870544434</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>8204</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Contulmo</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>39.2056312561035</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>8307</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Negrete</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>39.0093879699707</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>38.4587249755859</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>38.4034767150879</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>8104</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>38.2336463928223</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Nacimiento</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>37.9488563537598</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>8308</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Quilaco</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>37.8181076049805</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>8104</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>37.6941223144531</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>8314</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Alto Biobío</t>
         </is>
       </c>
-      <c r="C34">
+      <c r="C101">
+        <v>37.4971160888672</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>8307</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Negrete</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>37.353946685791</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>8308</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Quilaco</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>37.2106819152832</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>37.0337295532227</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>36.8649787902832</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>36.5858459472656</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Cabrero</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>36.5057678222656</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Quilleco</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>36.4299392700195</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hualqui</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>35.5565605163574</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>35.5107536315918</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Tomé</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>35.4734039306641</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Los Alamos</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>35.2649765014648</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Nacimiento</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>35.144645690918</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>35.0612831115723</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>34.89794921875</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>8202</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>34.3627014160156</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>34.2559204101562</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>33.8302001953125</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>33.7297477722168</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>8108</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>San Pedro de la Paz</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>33.6268615722656</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>33.6114082336426</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>San Rosendo</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>33.6014862060547</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>8314</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Alto Biobío</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>33.383113861084</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>8312</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Tucapel</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>33.3594779968262</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>33.1601524353027</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cabrero</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>33.0250015258789</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>8207</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Tirúa</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>32.9498672485352</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Quilleco</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>32.905876159668</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>32.7726707458496</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>8204</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Contulmo</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>32.680549621582</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>San Rosendo</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>32.6151123046875</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Santa Juana</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>32.5822257995605</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>31.9358654022217</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>31.8969688415527</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>31.5716400146484</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>8103</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Chiguayante</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>31.5346374511719</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>31.5081233978271</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Hualpén</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>31.5032196044922</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>31.4994831085205</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>8308</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Quilaco</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>31.4019088745117</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Hualpén</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>31.3229522705078</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>31.1425075531006</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>30.8749294281006</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Santa Juana</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>30.5809230804443</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>30.5155162811279</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Hualqui</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>30.5103282928467</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>30.3653583526611</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>8312</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Tucapel</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>30.3103847503662</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>8204</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Contulmo</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>29.9088973999023</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Tomé</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>29.8538818359375</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>8104</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>29.7146682739258</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>29.7015190124512</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>8103</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Chiguayante</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>29.5158576965332</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Antuco</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>29.0304393768311</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>28.8587474822998</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>28.7660083770752</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>28.4650268554688</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>28.4135608673096</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>28.213472366333</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>28.201114654541</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>8108</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>San Pedro de la Paz</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>28.1848106384277</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>8308</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Quilaco</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>28.1622905731201</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>8104</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>28.1418018341064</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>27.9324245452881</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>27.1030082702637</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Los Alamos</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>27.056396484375</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>8204</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Contulmo</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>27.0554676055908</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>8207</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Tirúa</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>26.9443035125732</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>8204</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Contulmo</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>26.7890777587891</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>8202</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>26.6586055755615</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Tomé</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>26.5373802185059</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>8207</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Tirúa</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>26.0736198425293</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>8202</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>26.0441608428955</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>8314</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Alto Biobío</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>25.6510410308838</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Los Alamos</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>25.4196186065674</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>25.3240070343018</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Hualqui</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>25.3161029815674</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>8207</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Tirúa</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>25.2663345336914</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>8314</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Alto Biobío</t>
+        </is>
+      </c>
+      <c r="C179">
         <v>25.10032081604</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Antuco</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>24.8254318237305</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>8307</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Negrete</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>24.7680511474609</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Nacimiento</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>24.6724662780762</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>24.0036449432373</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>23.8921241760254</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>23.7896671295166</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Cabrero</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>23.7020721435547</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>8314</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Alto Biobío</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>23.1332130432129</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>8312</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Tucapel</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>22.754337310791</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>22.2263431549072</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Santa Juana</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>22.1385383605957</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Quilleco</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>21.384557723999</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>San Rosendo</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>21.369083404541</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>8104</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>21.2862319946289</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>20.9485607147217</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>8207</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Tirúa</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>20.4618244171143</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>19.405818939209</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>8308</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Quilaco</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>19.0211963653564</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Antuco</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>18.961483001709</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>8314</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Alto Biobío</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>16.707103729248</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>16.559606552124</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>14.402928352356</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Los Alamos</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>13.7222385406494</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>13.5488576889038</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>8103</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Chiguayante</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>13.0365533828735</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>8108</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>San Pedro de la Paz</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>12.6830797195435</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>12.4797716140747</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>11.3634757995605</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>11.3407030105591</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Hualpén</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>10.5079336166382</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>10.3432016372681</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>8307</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Negrete</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>10.3107347488403</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Nacimiento</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>10.2481555938721</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Tomé</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>10.1231927871704</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>8202</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>9.83670043945312</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>9.80094623565674</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Hualqui</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>9.73883533477783</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>9.56770706176758</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>9.54767513275146</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>8207</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Tirúa</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>9.46087646484375</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Cabrero</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>8.87824153900146</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>8104</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>8.049135208129879</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>San Rosendo</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>7.92843675613403</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>8312</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Tucapel</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>7.78596258163452</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>7.74923419952393</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Santa Juana</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>7.4513578414917</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>8204</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Contulmo</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>7.17465305328369</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>8314</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Alto Biobío</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>7.09472846984863</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Quilleco</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>7.0181303024292</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Antuco</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>6.94731426239014</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>6.69915580749512</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>6.02969360351562</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>8308</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Quilaco</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>4.98633861541748</v>
       </c>
     </row>
   </sheetData>
